--- a/Verified_All_Quarters_Result_Dates_211_Stocks.xlsx
+++ b/Verified_All_Quarters_Result_Dates_211_Stocks.xlsx
@@ -11578,12 +11578,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F318" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G318" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F318" s="2" t="inlineStr"/>
+      <c r="G318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -11854,12 +11850,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F326" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G326" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F326" s="2" t="inlineStr"/>
+      <c r="G326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -18150,12 +18142,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F506" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G506" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F506" s="2" t="inlineStr"/>
+      <c r="G506" s="2" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
@@ -19546,12 +19534,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F546" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G546" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F546" s="2" t="inlineStr"/>
+      <c r="G546" s="2" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
@@ -25422,12 +25406,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F714" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G714" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F714" s="2" t="inlineStr"/>
+      <c r="G714" s="2" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
@@ -26923,12 +26903,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F757" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G757" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F757" s="2" t="inlineStr"/>
+      <c r="G757" s="2" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
@@ -33324,12 +33300,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F940" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G940" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F940" s="2" t="inlineStr"/>
+      <c r="G940" s="2" t="inlineStr"/>
     </row>
     <row r="941">
       <c r="A941" s="2" t="n">
@@ -34405,12 +34377,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F971" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G971" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F971" s="2" t="inlineStr"/>
+      <c r="G971" s="2" t="inlineStr"/>
     </row>
     <row r="972">
       <c r="A972" s="2" t="n">
@@ -39651,12 +39619,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1121" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1121" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1121" s="2" t="inlineStr"/>
+      <c r="G1121" s="2" t="inlineStr"/>
     </row>
     <row r="1122">
       <c r="A1122" s="2" t="n">
@@ -41642,12 +41606,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1178" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1178" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1178" s="2" t="inlineStr"/>
+      <c r="G1178" s="2" t="inlineStr"/>
     </row>
     <row r="1179">
       <c r="A1179" s="2" t="n">
@@ -42338,12 +42298,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1198" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1198" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1198" s="2" t="inlineStr"/>
+      <c r="G1198" s="2" t="inlineStr"/>
     </row>
     <row r="1199">
       <c r="A1199" s="2" t="n">
@@ -42544,12 +42500,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1204" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1204" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1204" s="2" t="inlineStr"/>
+      <c r="G1204" s="2" t="inlineStr"/>
     </row>
     <row r="1205">
       <c r="A1205" s="2" t="n">
@@ -42995,12 +42947,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1217" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1217" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1217" s="2" t="inlineStr"/>
+      <c r="G1217" s="2" t="inlineStr"/>
     </row>
     <row r="1218">
       <c r="A1218" s="2" t="n">
@@ -43026,12 +42974,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1218" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1218" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1218" s="2" t="inlineStr"/>
+      <c r="G1218" s="2" t="inlineStr"/>
     </row>
     <row r="1219">
       <c r="A1219" s="2" t="n">
@@ -43827,12 +43771,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1241" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1241" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1241" s="2" t="inlineStr"/>
+      <c r="G1241" s="2" t="inlineStr"/>
     </row>
     <row r="1242">
       <c r="A1242" s="2" t="n">
@@ -43858,12 +43798,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1242" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1242" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1242" s="2" t="inlineStr"/>
+      <c r="G1242" s="2" t="inlineStr"/>
     </row>
     <row r="1243">
       <c r="A1243" s="2" t="n">
@@ -44484,12 +44420,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1260" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1260" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1260" s="2" t="inlineStr"/>
+      <c r="G1260" s="2" t="inlineStr"/>
     </row>
     <row r="1261">
       <c r="A1261" s="2" t="n">
@@ -44550,12 +44482,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1262" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1262" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1262" s="2" t="inlineStr"/>
+      <c r="G1262" s="2" t="inlineStr"/>
     </row>
     <row r="1263">
       <c r="A1263" s="2" t="n">
@@ -46191,12 +46119,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1309" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1309" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1309" s="2" t="inlineStr"/>
+      <c r="G1309" s="2" t="inlineStr"/>
     </row>
     <row r="1310">
       <c r="A1310" s="2" t="n">
@@ -46222,12 +46146,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1310" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1310" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1310" s="2" t="inlineStr"/>
+      <c r="G1310" s="2" t="inlineStr"/>
     </row>
     <row r="1311">
       <c r="A1311" s="2" t="n">
@@ -46813,12 +46733,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1327" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1327" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1327" s="2" t="inlineStr"/>
+      <c r="G1327" s="2" t="inlineStr"/>
     </row>
     <row r="1328">
       <c r="A1328" s="2" t="n">
@@ -46844,12 +46760,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1328" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1328" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1328" s="2" t="inlineStr"/>
+      <c r="G1328" s="2" t="inlineStr"/>
     </row>
     <row r="1329">
       <c r="A1329" s="2" t="n">
@@ -47365,12 +47277,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1343" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1343" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1343" s="2" t="inlineStr"/>
+      <c r="G1343" s="2" t="inlineStr"/>
     </row>
     <row r="1344">
       <c r="A1344" s="2" t="n">
@@ -47431,12 +47339,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1345" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1345" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1345" s="2" t="inlineStr"/>
+      <c r="G1345" s="2" t="inlineStr"/>
     </row>
     <row r="1346">
       <c r="A1346" s="2" t="n">
@@ -47952,12 +47856,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1360" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1360" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1360" s="2" t="inlineStr"/>
+      <c r="G1360" s="2" t="inlineStr"/>
     </row>
     <row r="1361">
       <c r="A1361" s="2" t="n">
@@ -48123,12 +48023,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1365" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1365" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1365" s="2" t="inlineStr"/>
+      <c r="G1365" s="2" t="inlineStr"/>
     </row>
     <row r="1366">
       <c r="A1366" s="2" t="n">
@@ -48679,12 +48575,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1381" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1381" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1381" s="2" t="inlineStr"/>
+      <c r="G1381" s="2" t="inlineStr"/>
     </row>
     <row r="1382">
       <c r="A1382" s="2" t="n">
@@ -48710,12 +48602,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1382" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1382" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1382" s="2" t="inlineStr"/>
+      <c r="G1382" s="2" t="inlineStr"/>
     </row>
     <row r="1383">
       <c r="A1383" s="2" t="n">
@@ -49441,12 +49329,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1403" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1403" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1403" s="2" t="inlineStr"/>
+      <c r="G1403" s="2" t="inlineStr"/>
     </row>
     <row r="1404">
       <c r="A1404" s="2" t="n">
@@ -49472,12 +49356,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1404" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1404" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1404" s="2" t="inlineStr"/>
+      <c r="G1404" s="2" t="inlineStr"/>
     </row>
     <row r="1405">
       <c r="A1405" s="2" t="n">
@@ -49923,12 +49803,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1417" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1417" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1417" s="2" t="inlineStr"/>
+      <c r="G1417" s="2" t="inlineStr"/>
     </row>
     <row r="1418">
       <c r="A1418" s="2" t="n">
@@ -50059,12 +49935,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1421" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1421" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1421" s="2" t="inlineStr"/>
+      <c r="G1421" s="2" t="inlineStr"/>
     </row>
     <row r="1422">
       <c r="A1422" s="2" t="n">
@@ -50265,12 +50137,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1427" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1427" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1427" s="2" t="inlineStr"/>
+      <c r="G1427" s="2" t="inlineStr"/>
     </row>
     <row r="1428">
       <c r="A1428" s="2" t="n">
@@ -50366,12 +50234,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1430" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1430" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1430" s="2" t="inlineStr"/>
+      <c r="G1430" s="2" t="inlineStr"/>
     </row>
     <row r="1431">
       <c r="A1431" s="2" t="n">
@@ -50607,12 +50471,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1437" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1437" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1437" s="2" t="inlineStr"/>
+      <c r="G1437" s="2" t="inlineStr"/>
     </row>
     <row r="1438">
       <c r="A1438" s="2" t="n">
@@ -50743,12 +50603,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1441" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1441" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1441" s="2" t="inlineStr"/>
+      <c r="G1441" s="2" t="inlineStr"/>
     </row>
     <row r="1442">
       <c r="A1442" s="2" t="n">
@@ -51089,12 +50945,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1451" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1451" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1451" s="2" t="inlineStr"/>
+      <c r="G1451" s="2" t="inlineStr"/>
     </row>
     <row r="1452">
       <c r="A1452" s="2" t="n">
@@ -51155,12 +51007,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1453" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1453" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1453" s="2" t="inlineStr"/>
+      <c r="G1453" s="2" t="inlineStr"/>
     </row>
     <row r="1454">
       <c r="A1454" s="2" t="n">
@@ -51186,12 +51034,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1454" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1454" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1454" s="2" t="inlineStr"/>
+      <c r="G1454" s="2" t="inlineStr"/>
     </row>
     <row r="1455">
       <c r="A1455" s="2" t="n">
@@ -51532,12 +51376,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1464" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1464" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1464" s="2" t="inlineStr"/>
+      <c r="G1464" s="2" t="inlineStr"/>
     </row>
     <row r="1465">
       <c r="A1465" s="2" t="n">
@@ -51668,12 +51508,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1468" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1468" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1468" s="2" t="inlineStr"/>
+      <c r="G1468" s="2" t="inlineStr"/>
     </row>
     <row r="1469">
       <c r="A1469" s="2" t="n">
@@ -51909,12 +51745,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1475" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1475" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1475" s="2" t="inlineStr"/>
+      <c r="G1475" s="2" t="inlineStr"/>
     </row>
     <row r="1476">
       <c r="A1476" s="2" t="n">
@@ -51940,12 +51772,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1476" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1476" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1476" s="2" t="inlineStr"/>
+      <c r="G1476" s="2" t="inlineStr"/>
     </row>
     <row r="1477">
       <c r="A1477" s="2" t="n">
@@ -52216,12 +52044,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1484" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1484" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1484" s="2" t="inlineStr"/>
+      <c r="G1484" s="2" t="inlineStr"/>
     </row>
     <row r="1485">
       <c r="A1485" s="2" t="n">
@@ -52317,12 +52141,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1487" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1487" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1487" s="2" t="inlineStr"/>
+      <c r="G1487" s="2" t="inlineStr"/>
     </row>
     <row r="1488">
       <c r="A1488" s="2" t="n">
@@ -52733,12 +52553,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1499" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1499" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1499" s="2" t="inlineStr"/>
+      <c r="G1499" s="2" t="inlineStr"/>
     </row>
     <row r="1500">
       <c r="A1500" s="2" t="n">
@@ -52904,12 +52720,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1504" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1504" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1504" s="2" t="inlineStr"/>
+      <c r="G1504" s="2" t="inlineStr"/>
     </row>
     <row r="1505">
       <c r="A1505" s="2" t="n">
@@ -53110,12 +52922,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1510" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1510" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1510" s="2" t="inlineStr"/>
+      <c r="G1510" s="2" t="inlineStr"/>
     </row>
     <row r="1511">
       <c r="A1511" s="2" t="n">
@@ -53211,12 +53019,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1513" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1513" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1513" s="2" t="inlineStr"/>
+      <c r="G1513" s="2" t="inlineStr"/>
     </row>
     <row r="1514">
       <c r="A1514" s="2" t="n">
@@ -53452,12 +53256,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1520" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1520" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1520" s="2" t="inlineStr"/>
+      <c r="G1520" s="2" t="inlineStr"/>
     </row>
     <row r="1521">
       <c r="A1521" s="2" t="n">
@@ -53588,12 +53388,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1524" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1524" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1524" s="2" t="inlineStr"/>
+      <c r="G1524" s="2" t="inlineStr"/>
     </row>
     <row r="1525">
       <c r="A1525" s="2" t="n">
@@ -53934,12 +53730,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1534" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1534" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1534" s="2" t="inlineStr"/>
+      <c r="G1534" s="2" t="inlineStr"/>
     </row>
     <row r="1535">
       <c r="A1535" s="2" t="n">
@@ -54070,12 +53862,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1538" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1538" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1538" s="2" t="inlineStr"/>
+      <c r="G1538" s="2" t="inlineStr"/>
     </row>
     <row r="1539">
       <c r="A1539" s="2" t="n">
@@ -54241,12 +54029,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1543" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1543" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1543" s="2" t="inlineStr"/>
+      <c r="G1543" s="2" t="inlineStr"/>
     </row>
     <row r="1544">
       <c r="A1544" s="2" t="n">
@@ -54272,12 +54056,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1544" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1544" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1544" s="2" t="inlineStr"/>
+      <c r="G1544" s="2" t="inlineStr"/>
     </row>
     <row r="1545">
       <c r="A1545" s="2" t="n">
@@ -54478,12 +54258,8 @@
           <t>Audited</t>
         </is>
       </c>
-      <c r="F1550" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1550" s="2" t="n">
-        <v/>
-      </c>
+      <c r="F1550" s="2" t="inlineStr"/>
+      <c r="G1550" s="2" t="inlineStr"/>
     </row>
     <row r="1551">
       <c r="A1551" s="2" t="n">
